--- a/artfynd/A 61586-2023 artfynd.xlsx
+++ b/artfynd/A 61586-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126112456</v>
       </c>
       <c r="B2" t="n">
-        <v>57537</v>
+        <v>57538</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61586-2023 artfynd.xlsx
+++ b/artfynd/A 61586-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126112456</v>
       </c>
       <c r="B2" t="n">
-        <v>57538</v>
+        <v>57542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61586-2023 artfynd.xlsx
+++ b/artfynd/A 61586-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126112456</v>
       </c>
       <c r="B2" t="n">
-        <v>57542</v>
+        <v>57543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61586-2023 artfynd.xlsx
+++ b/artfynd/A 61586-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,6 +781,208 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131370838</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91871</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Svartbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>454128</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6570952</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Marcus Arnesson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Marcus Arnesson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131370845</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svartbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>454128</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6570952</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Marcus Arnesson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Marcus Arnesson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61586-2023 artfynd.xlsx
+++ b/artfynd/A 61586-2023 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>131370838</v>
       </c>
       <c r="B3" t="n">
-        <v>91871</v>
+        <v>91873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131370845</v>
       </c>
       <c r="B4" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61586-2023 artfynd.xlsx
+++ b/artfynd/A 61586-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,7 +787,7 @@
         <v>131370838</v>
       </c>
       <c r="B3" t="n">
-        <v>91873</v>
+        <v>91874</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131370845</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,6 +984,228 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131428704</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57833</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Plattberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>454491</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6570914</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marcus Arnesson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marcus Arnesson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131428710</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57824</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100082</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Röd glada</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Milvus milvus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Plattberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>454491</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6570914</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marcus Arnesson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Marcus Arnesson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61586-2023 artfynd.xlsx
+++ b/artfynd/A 61586-2023 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>131370838</v>
       </c>
       <c r="B3" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131370845</v>
       </c>
       <c r="B4" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>131428704</v>
       </c>
       <c r="B5" t="n">
-        <v>57838</v>
+        <v>57844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>131428710</v>
       </c>
       <c r="B6" t="n">
-        <v>57829</v>
+        <v>57835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61586-2023 artfynd.xlsx
+++ b/artfynd/A 61586-2023 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>131370838</v>
       </c>
       <c r="B3" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131370845</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>131428704</v>
       </c>
       <c r="B5" t="n">
-        <v>57844</v>
+        <v>57845</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>131428710</v>
       </c>
       <c r="B6" t="n">
-        <v>57835</v>
+        <v>57836</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61586-2023 artfynd.xlsx
+++ b/artfynd/A 61586-2023 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>131370838</v>
       </c>
       <c r="B3" t="n">
-        <v>91886</v>
+        <v>91889</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131370845</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>131428704</v>
       </c>
       <c r="B5" t="n">
-        <v>57845</v>
+        <v>57848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>131428710</v>
       </c>
       <c r="B6" t="n">
-        <v>57836</v>
+        <v>57839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61586-2023 artfynd.xlsx
+++ b/artfynd/A 61586-2023 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>131370838</v>
       </c>
       <c r="B3" t="n">
-        <v>91889</v>
+        <v>91895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131370845</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>131428704</v>
       </c>
       <c r="B5" t="n">
-        <v>57848</v>
+        <v>57850</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>131428710</v>
       </c>
       <c r="B6" t="n">
-        <v>57839</v>
+        <v>57841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61586-2023 artfynd.xlsx
+++ b/artfynd/A 61586-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126112456</v>
       </c>
       <c r="B2" t="n">
-        <v>57543</v>
+        <v>57791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61586-2023 artfynd.xlsx
+++ b/artfynd/A 61586-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126112456</v>
       </c>
       <c r="B2" t="n">
-        <v>57791</v>
+        <v>57792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>131428704</v>
       </c>
       <c r="B5" t="n">
-        <v>57850</v>
+        <v>57853</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>131428710</v>
       </c>
       <c r="B6" t="n">
-        <v>57841</v>
+        <v>57844</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61586-2023 artfynd.xlsx
+++ b/artfynd/A 61586-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126112456</v>
       </c>
       <c r="B2" t="n">
-        <v>57792</v>
+        <v>57797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>131428704</v>
       </c>
       <c r="B5" t="n">
-        <v>57853</v>
+        <v>57858</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>131428710</v>
       </c>
       <c r="B6" t="n">
-        <v>57844</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61586-2023 artfynd.xlsx
+++ b/artfynd/A 61586-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126112456</v>
       </c>
       <c r="B2" t="n">
-        <v>57797</v>
+        <v>57799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61586-2023 artfynd.xlsx
+++ b/artfynd/A 61586-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126112456</v>
       </c>
       <c r="B2" t="n">
-        <v>57833</v>
+        <v>57834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61586-2023 artfynd.xlsx
+++ b/artfynd/A 61586-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126112456</v>
       </c>
       <c r="B2" t="n">
-        <v>57834</v>
+        <v>57838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61586-2023 artfynd.xlsx
+++ b/artfynd/A 61586-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126112456</v>
+        <v>131370838</v>
       </c>
       <c r="B2" t="n">
-        <v>57838</v>
+        <v>91966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100100</v>
+        <v>5321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bivråk</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pernis apivorus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Plattberget, Vrm</t>
+          <t>Svartbergen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454491</v>
+        <v>454128</v>
       </c>
       <c r="R2" t="n">
-        <v>6570914</v>
+        <v>6570952</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -752,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131370838</v>
+        <v>131370845</v>
       </c>
       <c r="B3" t="n">
-        <v>91895</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,26 +787,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5321</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -866,7 +859,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -885,27 +877,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131370845</v>
+        <v>131428704</v>
       </c>
       <c r="B4" t="n">
-        <v>57901</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100067</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -913,21 +905,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svartbergen, Vrm</t>
+          <t>Plattberget, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454128</v>
+        <v>454491</v>
       </c>
       <c r="R4" t="n">
-        <v>6570952</v>
+        <v>6570914</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -954,12 +958,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,27 +990,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131428704</v>
+        <v>131428710</v>
       </c>
       <c r="B5" t="n">
-        <v>57858</v>
+        <v>57890</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100067</v>
+        <v>100082</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1019,11 +1023,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2K</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
@@ -1099,27 +1099,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131428710</v>
+        <v>126112456</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57860</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100082</v>
+        <v>100100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 61586-2023 artfynd.xlsx
+++ b/artfynd/A 61586-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131370838</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131370845</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131428704</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131428710</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,8 +1230,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126112456</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>